--- a/data/processed/leakage_report.xlsx
+++ b/data/processed/leakage_report.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="4">
     <font>
